--- a/output/pdf_financials_xlsx/CRC.xlsx
+++ b/output/pdf_financials_xlsx/CRC.xlsx
@@ -1953,10 +1953,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.098084</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.098084</v>
       </c>
     </row>
     <row r="93">
@@ -3062,7 +3062,11 @@
           <t>Warrants reserve 7</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CRC.xlsx
+++ b/output/pdf_financials_xlsx/CRC.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.042145</v>
+        <v>0.122332</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.858299</v>
+        <v>1.365678</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.673909</v>
+        <v>1.103086</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.042145</v>
+        <v>-0.122332</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.858299</v>
+        <v>-1.365678</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.673909</v>
+        <v>-1.103086</v>
       </c>
     </row>
     <row r="12">
@@ -2845,7 +2845,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -4497,7 +4501,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4506,10 +4510,10 @@
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>-1.365678</v>
+        <v>1.365678</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-1.103086</v>
+        <v>1.103086</v>
       </c>
     </row>
     <row r="59">
@@ -4993,14 +4997,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>-0.122332</v>
+        <v>0.122332</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>-1.365678</v>
+        <v>1.365678</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CRC.xlsx
+++ b/output/pdf_financials_xlsx/CRC.xlsx
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.013286</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.07759099999999999</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.06290999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -1532,13 +1532,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.02552</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.07904700000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.19135</v>
       </c>
     </row>
     <row r="68">
